--- a/api/templates/unused_modules_report/fr.xlsx
+++ b/api/templates/unused_modules_report/fr.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11207"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harshthakkar/Desktop/Projects/aspect/api/templates/unused_modules_report/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51221250-D149-C648-B5BA-1AF290C0308A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28000" windowHeight="14600" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28000" windowHeight="14600"/>
   </bookViews>
   <sheets>
-    <sheet name="Device with Unused module" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Device with Unused module" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Device with Unused module'!$A$8:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase">'Device with Unused module'!$A$8:$F$9</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>Appareils GeneXpert avec modules inutilisés</t>
+  </si>
+  <si>
+    <t>Plage de dates : &lt;Dates&gt;</t>
+  </si>
   <si>
     <t>&lt;StatesLabel&gt;:  &lt;States&gt;</t>
   </si>
@@ -34,6 +34,9 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+  </si>
+  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
@@ -43,6 +46,9 @@
     <t>Deployment</t>
   </si>
   <si>
+    <t>Série de l’instrument</t>
+  </si>
+  <si>
     <t xml:space="preserve"> &lt;StateLabel&gt;</t>
   </si>
   <si>
@@ -55,6 +61,9 @@
     <t>Total Modules</t>
   </si>
   <si>
+    <t>Nombre total de modules utilisés</t>
+  </si>
+  <si>
     <t>&lt;#&gt;</t>
   </si>
   <si>
@@ -77,72 +86,61 @@
   </si>
   <si>
     <t>&lt;modulesReporting&gt;</t>
-  </si>
-  <si>
-    <t>Appareils GeneXpert avec modules inutilisés</t>
-  </si>
-  <si>
-    <t>Plage de dates : &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t>Série de l’instrument</t>
-  </si>
-  <si>
-    <t>Nombre total de modules utilisés</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd;@"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <family val="2"/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <charset val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
+      <charset val="1"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -168,33 +166,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -205,97 +187,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="003CC0DD"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -564,9 +478,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.5"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
     <col min="2" max="2" width="28.6640625" customWidth="1"/>
@@ -579,96 +493,101 @@
     <col min="16384" max="16384" width="10.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4"/>
+    </row>
+    <row r="3" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="E9" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="11" t="s">
+      <c r="F9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="11" t="s">
+      <c r="G9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" t="s">
-        <v>16</v>
-      </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:F9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A8:F9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/unused_modules_report/fr.xlsx
+++ b/api/templates/unused_modules_report/fr.xlsx
@@ -183,12 +183,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -524,7 +525,7 @@
       <c r="B5" s="4"/>
     </row>
     <row r="6" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -534,48 +535,48 @@
       </c>
     </row>
     <row r="8" ht="17" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G9" t="s">

--- a/api/templates/unused_modules_report/fr.xlsx
+++ b/api/templates/unused_modules_report/fr.xlsx
@@ -34,7 +34,7 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Dispositifs déclassés: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -183,13 +183,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -525,7 +524,7 @@
       <c r="B5" s="4"/>
     </row>
     <row r="6" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -535,48 +534,48 @@
       </c>
     </row>
     <row r="8" ht="17" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="10" t="s">
         <v>20</v>
       </c>
       <c r="G9" t="s">
